--- a/1.0.0-ballot/StructureDefinition-onko-care-plan.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:36:35+00:00</t>
+    <t>2026-07-30T15:22:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-care-plan.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T15:22:14+00:00</t>
+    <t>2026-07-31T08:51:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-care-plan.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T08:51:02+00:00</t>
+    <t>2026-07-31T12:16:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-care-plan.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-care-plan.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$64</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2318" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2354" uniqueCount="498">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:16:37+00:00</t>
+    <t>2026-07-31T12:21:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -503,6 +503,25 @@
     <t>Für Pflege und Aktualisierung des Plans verantwortliche Stelle – R5-Backport aus MCC.</t>
   </si>
   <si>
+    <t>CarePlan.extension:episodeOfCare</t>
+  </si>
+  <si>
+    <t>episodeOfCare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {workflow-episodeOfCare}
+</t>
+  </si>
+  <si>
+    <t>Behandlungsepisode</t>
+  </si>
+  <si>
+    <t>Behandlungsepisode bzw. Therapielinie, in deren Rahmen der Plan umgesetzt wird.</t>
+  </si>
+  <si>
+    <t>.inboundRelationship(typeCode=COMP].source[classCode&lt;=PCPR, moodCode=EVN]</t>
+  </si>
+  <si>
     <t>CarePlan.modifierExtension</t>
   </si>
   <si>
@@ -685,10 +704,10 @@
     <t>CarePlan.intent</t>
   </si>
   <si>
-    <t>proposal | plan | order | option</t>
-  </si>
-  <si>
-    <t>Indicates the level of authority/intentionality associated with the care plan and where the care plan fits into the workflow chain.</t>
+    <t>Planart</t>
+  </si>
+  <si>
+    <t>Art des Plans – proposal/plan = Empfehlungsplan des Tumorboards, plan/order = Behandlungsplan.</t>
   </si>
   <si>
     <t>This element is labeled as a modifier because the intent alters when and how the resource is actually applicable.</t>
@@ -1883,12 +1902,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN63"/>
+  <dimension ref="A1:AN64"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="36.58203125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="36.58203125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.66796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="12.5078125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -3181,48 +3200,46 @@
         <v>80</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>151</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="C12" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="D12" t="s" s="2">
-        <v>152</v>
+        <v>80</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J12" t="s" s="2">
         <v>80</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="N12" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="O12" t="s" s="2">
-        <v>156</v>
-      </c>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>80</v>
       </c>
@@ -3270,7 +3287,7 @@
         <v>80</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -3279,7 +3296,7 @@
         <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>80</v>
+        <v>145</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>139</v>
@@ -3288,7 +3305,7 @@
         <v>80</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>131</v>
+        <v>156</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>80</v>
@@ -3299,14 +3316,14 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>80</v>
+        <v>158</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -3319,25 +3336,25 @@
         <v>80</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="N13" t="s" s="2">
+      <c r="O13" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="O13" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>80</v>
@@ -3386,7 +3403,7 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -3398,27 +3415,27 @@
         <v>80</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AM13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN13" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" hidden="true">
+      <c r="A14" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="AL13" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="2">
-        <v>168</v>
-      </c>
       <c r="B14" t="s" s="2">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3432,7 +3449,7 @@
         <v>79</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>80</v>
@@ -3441,16 +3458,20 @@
         <v>89</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N14" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="O14" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="L14" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>80</v>
       </c>
@@ -3498,7 +3519,7 @@
         <v>80</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3513,19 +3534,19 @@
         <v>100</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AM14" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="AL14" t="s" s="2">
+      <c r="AN14" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="AM14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>80</v>
-      </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>174</v>
       </c>
@@ -3544,7 +3565,7 @@
         <v>79</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>80</v>
@@ -3553,17 +3574,15 @@
         <v>89</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>102</v>
+        <v>175</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N15" t="s" s="2">
         <v>177</v>
       </c>
+      <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>80</v>
@@ -3630,7 +3649,7 @@
         <v>178</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>80</v>
@@ -3641,14 +3660,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>180</v>
+        <v>80</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3667,18 +3686,18 @@
         <v>89</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="N16" s="2"/>
-      <c r="O16" t="s" s="2">
-        <v>184</v>
-      </c>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>80</v>
       </c>
@@ -3726,7 +3745,7 @@
         <v>80</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3741,10 +3760,10 @@
         <v>100</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>80</v>
+        <v>179</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>80</v>
@@ -3755,14 +3774,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3781,7 +3800,7 @@
         <v>89</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="L17" t="s" s="2">
         <v>188</v>
@@ -3789,11 +3808,9 @@
       <c r="M17" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="N17" s="2"/>
+      <c r="O17" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>80</v>
@@ -3842,7 +3859,7 @@
         <v>80</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3857,7 +3874,7 @@
         <v>100</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>80</v>
@@ -3871,14 +3888,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>80</v>
+        <v>193</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3897,7 +3914,7 @@
         <v>89</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="L18" t="s" s="2">
         <v>194</v>
@@ -3908,7 +3925,9 @@
       <c r="N18" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="O18" s="2"/>
+      <c r="O18" t="s" s="2">
+        <v>197</v>
+      </c>
       <c r="P18" t="s" s="2">
         <v>80</v>
       </c>
@@ -3956,7 +3975,7 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3971,7 +3990,7 @@
         <v>100</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>80</v>
@@ -3983,12 +4002,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3996,35 +4015,33 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J19" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>108</v>
+        <v>187</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>200</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>80</v>
       </c>
@@ -4048,13 +4065,13 @@
         <v>80</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>201</v>
+        <v>80</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>202</v>
+        <v>80</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>203</v>
+        <v>80</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>80</v>
@@ -4072,13 +4089,13 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>80</v>
@@ -4087,24 +4104,24 @@
         <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>204</v>
+        <v>80</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>205</v>
+        <v>80</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>206</v>
+        <v>80</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>207</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4118,7 +4135,7 @@
         <v>88</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>89</v>
@@ -4130,16 +4147,16 @@
         <v>108</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>209</v>
+        <v>10</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>80</v>
@@ -4164,13 +4181,13 @@
         <v>80</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>80</v>
@@ -4188,7 +4205,7 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>88</v>
@@ -4203,24 +4220,24 @@
         <v>100</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>80</v>
+        <v>211</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>80</v>
+        <v>212</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>80</v>
+        <v>213</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4228,34 +4245,34 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>89</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="J21" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="N21" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="O21" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>80</v>
@@ -4280,13 +4297,13 @@
         <v>80</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>80</v>
@@ -4304,13 +4321,13 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>80</v>
@@ -4319,24 +4336,24 @@
         <v>100</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>80</v>
+        <v>221</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>225</v>
+        <v>80</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4347,10 +4364,10 @@
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>80</v>
@@ -4359,16 +4376,20 @@
         <v>89</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="O22" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="L22" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>80</v>
       </c>
@@ -4392,13 +4413,13 @@
         <v>80</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>80</v>
+        <v>228</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>80</v>
+        <v>229</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>80</v>
+        <v>230</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>80</v>
@@ -4416,13 +4437,13 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>80</v>
@@ -4437,7 +4458,7 @@
         <v>80</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>80</v>
+        <v>231</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>80</v>
@@ -4445,10 +4466,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4471,18 +4492,16 @@
         <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="N23" s="2"/>
-      <c r="O23" t="s" s="2">
-        <v>233</v>
-      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>80</v>
       </c>
@@ -4530,7 +4549,7 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4551,32 +4570,32 @@
         <v>80</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>234</v>
+        <v>80</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>236</v>
+        <v>80</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>80</v>
@@ -4585,16 +4604,18 @@
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" s="2"/>
+      <c r="O24" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>80</v>
       </c>
@@ -4642,10 +4663,10 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>88</v>
@@ -4657,38 +4678,38 @@
         <v>100</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="AL24" t="s" s="2">
+      <c r="AN24" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="AM24" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="25" hidden="true">
-      <c r="A25" t="s" s="2">
-        <v>244</v>
-      </c>
       <c r="B25" t="s" s="2">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>80</v>
+        <v>242</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>80</v>
@@ -4697,17 +4718,15 @@
         <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="L25" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>248</v>
-      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>80</v>
@@ -4756,10 +4775,10 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>88</v>
@@ -4771,28 +4790,28 @@
         <v>100</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>252</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>254</v>
+        <v>80</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4811,20 +4830,18 @@
         <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>80</v>
       </c>
@@ -4872,7 +4889,7 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4887,28 +4904,28 @@
         <v>100</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>263</v>
+        <v>258</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4927,16 +4944,20 @@
         <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>80</v>
       </c>
@@ -4984,7 +5005,7 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4999,28 +5020,28 @@
         <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="AL27" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>80</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>80</v>
+        <v>271</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5039,17 +5060,15 @@
         <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="M28" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>276</v>
-      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>80</v>
@@ -5098,7 +5117,7 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5113,24 +5132,24 @@
         <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AM28" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="AL28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AN28" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="29" hidden="true">
+      <c r="A29" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="AN28" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s" s="2">
-        <v>279</v>
-      </c>
       <c r="B29" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5141,19 +5160,19 @@
         <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J29" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J29" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="K29" t="s" s="2">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="L29" t="s" s="2">
         <v>280</v>
@@ -5212,13 +5231,13 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>80</v>
@@ -5227,13 +5246,13 @@
         <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>80</v>
+        <v>283</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>80</v>
+        <v>284</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>80</v>
@@ -5241,10 +5260,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5267,18 +5286,18 @@
         <v>80</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="N30" s="2"/>
-      <c r="O30" t="s" s="2">
         <v>287</v>
       </c>
+      <c r="N30" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>80</v>
       </c>
@@ -5326,7 +5345,7 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5341,13 +5360,13 @@
         <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>288</v>
+        <v>80</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>289</v>
+        <v>80</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>80</v>
@@ -5355,10 +5374,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5366,7 +5385,7 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>79</v>
@@ -5378,22 +5397,20 @@
         <v>80</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" s="2"/>
+      <c r="O31" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>80</v>
@@ -5442,7 +5459,7 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5457,24 +5474,24 @@
         <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>297</v>
+        <v>80</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>299</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5482,7 +5499,7 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>79</v>
@@ -5494,22 +5511,22 @@
         <v>80</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="O32" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="L32" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>80</v>
@@ -5558,7 +5575,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5573,24 +5590,24 @@
         <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>80</v>
+        <v>303</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>80</v>
+        <v>304</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>80</v>
+        <v>305</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5613,19 +5630,19 @@
         <v>80</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="N33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>80</v>
@@ -5674,7 +5691,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5689,24 +5706,24 @@
         <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>80</v>
+        <v>312</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>313</v>
+        <v>80</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>314</v>
+        <v>80</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5729,17 +5746,19 @@
         <v>80</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>80</v>
@@ -5788,7 +5807,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5800,27 +5819,27 @@
         <v>80</v>
       </c>
       <c r="AJ34" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="AK34" t="s" s="2">
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="AL34" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="35" hidden="true">
-      <c r="A35" t="s" s="2">
-        <v>323</v>
-      </c>
       <c r="B35" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5831,10 +5850,10 @@
         <v>78</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>80</v>
@@ -5843,16 +5862,18 @@
         <v>80</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>227</v>
+        <v>322</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" s="2"/>
+      <c r="O35" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>80</v>
       </c>
@@ -5900,25 +5921,25 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="AG35" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH35" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ35" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="AK35" t="s" s="2">
-        <v>80</v>
+        <v>327</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>80</v>
@@ -5929,21 +5950,21 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>152</v>
+        <v>80</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>80</v>
@@ -5955,17 +5976,15 @@
         <v>80</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>133</v>
+        <v>233</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>155</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>80</v>
@@ -6014,25 +6033,25 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>139</v>
+        <v>80</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>80</v>
@@ -6043,14 +6062,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>333</v>
+        <v>158</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6063,26 +6082,24 @@
         <v>80</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K37" t="s" s="2">
         <v>133</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>156</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>80</v>
       </c>
@@ -6130,7 +6147,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6148,7 +6165,7 @@
         <v>80</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>131</v>
+        <v>333</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>80</v>
@@ -6159,14 +6176,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>80</v>
+        <v>339</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6179,24 +6196,26 @@
         <v>80</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>217</v>
+        <v>133</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>161</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>80</v>
       </c>
@@ -6220,31 +6239,31 @@
         <v>80</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>222</v>
+        <v>80</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>341</v>
+        <v>80</v>
       </c>
       <c r="Z38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF38" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="AA38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6256,13 +6275,13 @@
         <v>80</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>80</v>
+        <v>131</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>80</v>
@@ -6271,7 +6290,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
         <v>343</v>
       </c>
@@ -6290,7 +6309,7 @@
         <v>79</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>80</v>
@@ -6299,20 +6318,18 @@
         <v>80</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="N39" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>348</v>
-      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>80</v>
       </c>
@@ -6336,13 +6353,13 @@
         <v>80</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>80</v>
+        <v>228</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>80</v>
+        <v>347</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>80</v>
+        <v>348</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>80</v>
@@ -6375,24 +6392,24 @@
         <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="AL39" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="40" hidden="true">
-      <c r="A40" t="s" s="2">
-        <v>351</v>
-      </c>
       <c r="B40" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6406,7 +6423,7 @@
         <v>79</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>80</v>
@@ -6415,19 +6432,19 @@
         <v>80</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>80</v>
@@ -6476,7 +6493,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6491,24 +6508,24 @@
         <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>80</v>
+        <v>355</v>
       </c>
       <c r="AL40" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN40" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="41" hidden="true">
+      <c r="A41" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="AM40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s" s="2">
-        <v>359</v>
-      </c>
       <c r="B41" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6519,10 +6536,10 @@
         <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>80</v>
@@ -6531,19 +6548,19 @@
         <v>80</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>80</v>
@@ -6592,39 +6609,39 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>365</v>
+        <v>80</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>366</v>
+        <v>80</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>322</v>
+        <v>363</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>80</v>
+        <v>364</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6638,7 +6655,7 @@
         <v>88</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>80</v>
@@ -6647,15 +6664,17 @@
         <v>80</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>316</v>
+        <v>366</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
         <v>370</v>
       </c>
@@ -6706,7 +6725,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6715,16 +6734,16 @@
         <v>88</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>80</v>
+        <v>372</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>371</v>
+        <v>328</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>80</v>
@@ -6735,10 +6754,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6761,16 +6780,18 @@
         <v>80</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>227</v>
+        <v>322</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>324</v>
+        <v>374</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>325</v>
+        <v>375</v>
       </c>
       <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+      <c r="O43" t="s" s="2">
+        <v>376</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>80</v>
       </c>
@@ -6818,7 +6839,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>326</v>
+        <v>373</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6827,16 +6848,16 @@
         <v>88</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>80</v>
+        <v>371</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>327</v>
+        <v>377</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>80</v>
@@ -6847,21 +6868,21 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>152</v>
+        <v>80</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>80</v>
@@ -6873,17 +6894,15 @@
         <v>80</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>133</v>
+        <v>233</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>155</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>80</v>
@@ -6932,25 +6951,25 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>139</v>
+        <v>80</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>80</v>
@@ -6961,14 +6980,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>333</v>
+        <v>158</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6981,26 +7000,24 @@
         <v>80</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K45" t="s" s="2">
         <v>133</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>156</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>80</v>
       </c>
@@ -7048,7 +7065,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7066,7 +7083,7 @@
         <v>80</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>131</v>
+        <v>333</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>80</v>
@@ -7077,43 +7094,45 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>80</v>
+        <v>339</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>376</v>
+        <v>340</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>341</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="O46" t="s" s="2">
-        <v>378</v>
+        <v>162</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>80</v>
@@ -7138,13 +7157,13 @@
         <v>80</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>201</v>
+        <v>80</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>379</v>
+        <v>80</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>380</v>
+        <v>80</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>80</v>
@@ -7162,25 +7181,25 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>375</v>
+        <v>342</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>381</v>
+        <v>131</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>80</v>
@@ -7191,10 +7210,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7205,7 +7224,7 @@
         <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>80</v>
@@ -7217,17 +7236,17 @@
         <v>80</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="L47" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>80</v>
@@ -7252,13 +7271,13 @@
         <v>80</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>80</v>
+        <v>207</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>80</v>
+        <v>385</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>80</v>
+        <v>386</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>80</v>
@@ -7276,13 +7295,13 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>80</v>
@@ -7291,10 +7310,10 @@
         <v>100</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>172</v>
+        <v>80</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>173</v>
+        <v>387</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>80</v>
@@ -7305,10 +7324,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7331,19 +7350,17 @@
         <v>80</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>102</v>
+        <v>389</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>175</v>
+        <v>390</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>177</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>80</v>
@@ -7392,7 +7409,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7410,7 +7427,7 @@
         <v>178</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>80</v>
@@ -7421,10 +7438,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7435,7 +7452,7 @@
         <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>80</v>
@@ -7447,19 +7464,19 @@
         <v>80</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>217</v>
+        <v>102</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>390</v>
+        <v>181</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="N49" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="O49" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>80</v>
@@ -7484,13 +7501,13 @@
         <v>80</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>222</v>
+        <v>80</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>394</v>
+        <v>80</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>395</v>
+        <v>80</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>80</v>
@@ -7508,13 +7525,13 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>80</v>
@@ -7523,24 +7540,24 @@
         <v>100</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>396</v>
+        <v>184</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>397</v>
+        <v>179</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>398</v>
+        <v>80</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7551,7 +7568,7 @@
         <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>80</v>
@@ -7563,18 +7580,20 @@
         <v>80</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="O50" s="2"/>
+        <v>398</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>399</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>80</v>
       </c>
@@ -7598,13 +7617,13 @@
         <v>80</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>80</v>
@@ -7622,13 +7641,13 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>80</v>
@@ -7637,24 +7656,24 @@
         <v>100</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>80</v>
+        <v>403</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>80</v>
+        <v>404</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7677,16 +7696,16 @@
         <v>80</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7712,13 +7731,13 @@
         <v>80</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>80</v>
+        <v>228</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>80</v>
+        <v>409</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>80</v>
+        <v>410</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>80</v>
@@ -7736,7 +7755,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7751,7 +7770,7 @@
         <v>100</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>296</v>
+        <v>411</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>80</v>
@@ -7765,10 +7784,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7791,18 +7810,18 @@
         <v>80</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" t="s" s="2">
         <v>415</v>
       </c>
+      <c r="N52" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>80</v>
       </c>
@@ -7850,7 +7869,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7865,10 +7884,10 @@
         <v>100</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>80</v>
+        <v>302</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>313</v>
+        <v>80</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>80</v>
@@ -7879,10 +7898,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7890,34 +7909,32 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>108</v>
+        <v>418</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>419</v>
-      </c>
+        <v>420</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>80</v>
@@ -7942,13 +7959,13 @@
         <v>80</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>201</v>
+        <v>80</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>421</v>
+        <v>80</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>422</v>
+        <v>80</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>80</v>
@@ -7966,13 +7983,13 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>80</v>
@@ -7981,24 +7998,24 @@
         <v>100</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>423</v>
+        <v>80</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>424</v>
+        <v>319</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>425</v>
+        <v>80</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8006,7 +8023,7 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>88</v>
@@ -8015,24 +8032,26 @@
         <v>80</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="J54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>217</v>
+        <v>108</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>425</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>426</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>80</v>
       </c>
@@ -8056,13 +8075,13 @@
         <v>80</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>80</v>
+        <v>207</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>80</v>
+        <v>427</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>80</v>
+        <v>428</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>80</v>
@@ -8080,10 +8099,10 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH54" t="s" s="2">
         <v>88</v>
@@ -8095,24 +8114,24 @@
         <v>100</v>
       </c>
       <c r="AK54" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AL54" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="AL54" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="AM54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>80</v>
+        <v>431</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8129,13 +8148,13 @@
         <v>80</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>432</v>
+        <v>223</v>
       </c>
       <c r="L55" t="s" s="2">
         <v>433</v>
@@ -8146,15 +8165,11 @@
       <c r="N55" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="O55" t="s" s="2">
-        <v>436</v>
-      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="Q55" t="s" s="2">
-        <v>437</v>
-      </c>
+      <c r="Q55" s="2"/>
       <c r="R55" t="s" s="2">
         <v>80</v>
       </c>
@@ -8198,7 +8213,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8213,10 +8228,10 @@
         <v>100</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>439</v>
+        <v>80</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>80</v>
@@ -8227,10 +8242,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8247,28 +8262,32 @@
         <v>80</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="J56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="N56" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="O56" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="P56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q56" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="N56" s="2"/>
-      <c r="O56" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="P56" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q56" s="2"/>
       <c r="R56" t="s" s="2">
         <v>80</v>
       </c>
@@ -8312,7 +8331,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8327,16 +8346,16 @@
         <v>100</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>260</v>
+        <v>444</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>261</v>
+        <v>445</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>445</v>
+        <v>80</v>
       </c>
     </row>
     <row r="57" hidden="true">
@@ -8375,11 +8394,9 @@
       <c r="M57" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="N57" t="s" s="2">
+      <c r="N57" s="2"/>
+      <c r="O57" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>80</v>
@@ -8443,24 +8460,24 @@
         <v>100</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>80</v>
+        <v>266</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>452</v>
+        <v>267</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8471,7 +8488,7 @@
         <v>78</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>80</v>
@@ -8483,19 +8500,19 @@
         <v>80</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>80</v>
@@ -8544,13 +8561,13 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>80</v>
@@ -8559,24 +8576,24 @@
         <v>100</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN58" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>461</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8587,7 +8604,7 @@
         <v>78</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>80</v>
@@ -8599,16 +8616,20 @@
         <v>80</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="M59" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+      <c r="O59" t="s" s="2">
+        <v>457</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>80</v>
       </c>
@@ -8632,13 +8653,13 @@
         <v>80</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>222</v>
+        <v>80</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>466</v>
+        <v>80</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>467</v>
+        <v>80</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>80</v>
@@ -8656,13 +8677,13 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>80</v>
@@ -8671,28 +8692,28 @@
         <v>100</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>80</v>
+        <v>465</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>471</v>
+        <v>80</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8711,18 +8732,16 @@
         <v>80</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="N60" s="2"/>
-      <c r="O60" t="s" s="2">
-        <v>475</v>
-      </c>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>80</v>
       </c>
@@ -8746,13 +8765,13 @@
         <v>80</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>80</v>
+        <v>228</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>80</v>
+        <v>472</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>80</v>
+        <v>473</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>80</v>
@@ -8770,7 +8789,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8788,25 +8807,25 @@
         <v>80</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>80</v>
+        <v>477</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -8825,7 +8844,7 @@
         <v>80</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="L61" t="s" s="2">
         <v>479</v>
@@ -8834,7 +8853,9 @@
         <v>480</v>
       </c>
       <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
+      <c r="O61" t="s" s="2">
+        <v>481</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>80</v>
       </c>
@@ -8882,7 +8903,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8900,21 +8921,21 @@
         <v>80</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8937,13 +8958,13 @@
         <v>80</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>227</v>
+        <v>478</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8994,7 +9015,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9012,21 +9033,21 @@
         <v>80</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>358</v>
+        <v>488</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9037,7 +9058,7 @@
         <v>78</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>80</v>
@@ -9049,18 +9070,16 @@
         <v>80</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>352</v>
+        <v>233</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="N63" s="2"/>
-      <c r="O63" t="s" s="2">
-        <v>490</v>
-      </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>80</v>
       </c>
@@ -9108,13 +9127,13 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>80</v>
@@ -9123,20 +9142,134 @@
         <v>100</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>491</v>
+        <v>80</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>357</v>
+        <v>492</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN63" t="s" s="2">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K64" t="s" s="2">
         <v>358</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="P64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>364</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN63">
+  <autoFilter ref="A1:AN64">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9146,7 +9279,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI62">
+  <conditionalFormatting sqref="A2:AI63">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/1.0.0-ballot/StructureDefinition-onko-care-plan.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:21:47+00:00</t>
+    <t>2026-07-31T12:58:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-care-plan.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:58:15+00:00</t>
+    <t>2026-07-31T13:16:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-care-plan.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:16:40+00:00</t>
+    <t>2026-07-31T13:26:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-care-plan.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:26:52+00:00</t>
+    <t>2026-07-31T13:33:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-care-plan.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:33:02+00:00</t>
+    <t>2026-07-31T13:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-care-plan.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:38:59+00:00</t>
+    <t>2026-07-31T13:45:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-care-plan.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:45:11+00:00</t>
+    <t>2026-07-31T14:14:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -94,8 +94,8 @@
 - Therapieintention über die Extension `onko-therapy-intent` (kurativ, neoadjuvant, adjuvant,
   Erhaltung, palliativ, supportiv).
 - `goal` referenziert das Profil `OnkoTherapyGoal`.
-- Therapielinien (`OnkoTherapyLine`, Basis `EpisodeOfCare`) werden über `CarePlan.encounter`
-  bzw. die Standard-Extension `workflow-episodeOfCare` verknüpft.
+- Therapielinien (`OnkoTherapyLine`, Basis `EpisodeOfCare`) werden über die
+  Standard-Extension `workflow-episodeOfCare` verknüpft.
 Im Fallback-Pfad (keine computable Leitlinie) ist der CarePlan die führende Repräsentation des
 realen Versorgungsverlaufs; im Primärpfad referenziert er via `instantiatesCanonical` eine
 `PlanDefinition` aus dem CPG-on-FHIR-Stack.</t>

--- a/1.0.0-ballot/StructureDefinition-onko-care-plan.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T14:14:54+00:00</t>
+    <t>2026-07-31T14:25:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-care-plan.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T14:25:45+00:00</t>
+    <t>2026-08-02T18:42:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-care-plan.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-02T18:42:01+00:00</t>
+    <t>2026-08-02T18:51:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-care-plan.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-02T18:51:55+00:00</t>
+    <t>2026-08-03T05:20:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
